--- a/AAII_Financials/Quarterly/TT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>TT</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6353500</v>
+      </c>
+      <c r="E8" s="3">
         <v>4969400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5144500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5742500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5746400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4688500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4874000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5441200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5307400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4215500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4424100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4882900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4704700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3665800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4073800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4371900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4190400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3355500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3569300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3719800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3829700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3017600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3179100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3495500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3138800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2641300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3183700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3470900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3617600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2803700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3895100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4030900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>4357700</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4093800</v>
+      </c>
+      <c r="E9" s="3">
         <v>3241300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3390600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3624300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3585800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3011000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3163200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3466800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3371900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2755600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2952800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3224800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3120300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2522300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2854300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2939100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2867000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2366500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2523900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2514600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2558200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2062600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2229000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2357500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2152200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1888500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2257200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2352600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2452600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1985800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2727500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2714000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2959500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2259700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1728100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1753900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2118200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2160600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1677500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1710800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1974400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1935500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1459900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1471300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1658100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1584400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1143500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1219500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1432800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1323400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>989000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1045400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1205200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1271500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>955000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>950100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1138000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>986600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>752800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>926500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1118300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1165000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>817900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1167600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1316900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1398200</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,19 +1152,20 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>347600</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1159,11 +1173,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>309600</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1171,11 +1185,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>252300</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,52 +1358,55 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>-61200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-16100</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-8900</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2700</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1397,98 +1417,101 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>7300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>7900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>37500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>25600</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>16600</v>
       </c>
       <c r="AD14" s="3">
         <v>16600</v>
       </c>
       <c r="AE14" s="3">
+        <v>16600</v>
+      </c>
+      <c r="AF14" s="3">
         <v>13300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>6100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>21800</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>20100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>110000</v>
+      </c>
+      <c r="E15" s="3">
         <v>101100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>56000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>88300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>98100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>99100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>58500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>95000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>96200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>91500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>51400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>92000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>88400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>79800</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5130400</v>
+      </c>
+      <c r="E17" s="3">
         <v>4198100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4347000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4581400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4586400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3935700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4085000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4420300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4284800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3584400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3741500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4023400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3876000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3211900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3493200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3632400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3479800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2967300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3133600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3136400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3178700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2664400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2791100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2928600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2715300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2486900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2853500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2934400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3050700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2567200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3448400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3443900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3717400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1223100</v>
+      </c>
+      <c r="E18" s="3">
         <v>771300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>797500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1161100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1160000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>752800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>789000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1020900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1022600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>631100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>682600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>859500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>828700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>453900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>580600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>739500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>710600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>388200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>435700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>583400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>651000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>353200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>388000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>566900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>423500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>154400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>330200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>536500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>566900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>236500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>446700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>587000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>640300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,215 +1849,222 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-15500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>15000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>6800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>26000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-18700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>14900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>12500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-20400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-8500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1323200</v>
+      </c>
+      <c r="E21" s="3">
         <v>887900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>847600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1234400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1248200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>845600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>841400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1110600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1112000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>696600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>719300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>942600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>913500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>525500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>660900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>804700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>788800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>464800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>527000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>648700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>726100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>422000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>455100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>636900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>497300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>241900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>429100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>635600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>666600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>307800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>514800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>663700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>731200</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>55600</v>
+        <v>53100</v>
       </c>
       <c r="E22" s="3">
         <v>55600</v>
@@ -2033,296 +2073,305 @@
         <v>55600</v>
       </c>
       <c r="G22" s="3">
+        <v>55600</v>
+      </c>
+      <c r="H22" s="3">
         <v>57400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>58100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>59900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>63000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>57500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>58100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>57400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>57900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>61600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>57600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>55900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>55800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>55900</v>
-      </c>
-      <c r="T22" s="3">
-        <v>56000</v>
       </c>
       <c r="U22" s="3">
         <v>56000</v>
       </c>
       <c r="V22" s="3">
+        <v>56000</v>
+      </c>
+      <c r="W22" s="3">
         <v>57700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>59300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>60700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>61900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>62400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>61300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>63100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>63400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>63900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>64500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>51000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>49000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>48500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1163100</v>
+      </c>
+      <c r="E23" s="3">
         <v>735800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>741300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1091700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1092700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>752900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>750600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>967900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>972600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>550700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>614800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>796300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>766400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>389800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>522400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>665000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>653100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>331500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>394600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>518800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>592000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>285300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>322600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>500000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>361800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>103800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>260100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>466800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>504500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>167500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>377300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>530000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>586500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>218200</v>
+      </c>
+      <c r="E24" s="3">
         <v>136300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>122800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>231500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>216700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>134900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>135300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>181100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>205800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>105500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>98200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>157500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>169600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>73200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>73500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>104700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>136600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>61100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>65500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>96800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>122800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>48400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>72400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>89900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>83500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>51000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>46000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>80500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>91900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>20200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>130400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>128000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>944900</v>
+      </c>
+      <c r="E26" s="3">
         <v>599500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>618500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>860200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>876000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>618000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>615300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>786800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>766800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>445200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>516600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>638800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>596800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>316600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>448900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>560300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>516500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>270400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>329100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>422000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>469200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>236900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>250200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>410100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>278300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>52800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>214100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>386300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>412600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>147300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>246900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>531100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>458500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>925700</v>
+      </c>
+      <c r="E27" s="3">
         <v>584400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>591300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>847600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>874800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>604900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>604300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>772000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>755300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>436300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>504300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>626300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>586200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>307100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>444000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>555800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>510900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>267200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>325800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>419000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>464900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>234300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>245700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>406100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>275400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>50000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>209200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>382600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>409100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>144200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>239500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>526800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>454000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,109 +2783,115 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E29" s="3">
         <v>-10000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-21600</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-9400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>2900</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-8900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-3400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-8900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-6900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-5400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-9000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-6500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-6100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-4900</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-7900</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-7000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-8000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-13300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>900</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-36600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-79200</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>86900</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>76200</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>47000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>55700</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>14500</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E32" s="3">
         <v>15500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-15000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-6800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-26000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>18700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-14900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-12500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>18000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>20400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>8500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>925700</v>
+      </c>
+      <c r="E33" s="3">
         <v>584400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>591300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>847600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>874800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>604900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>604300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>772000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>755300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>436300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>504300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>626300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>586200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>307100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>439100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>547900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>509300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>260200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>317800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>405700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>464700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>235200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>244700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>400600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>238800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>296100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>458800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>456100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>199900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>254000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>515100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>448100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>925700</v>
+      </c>
+      <c r="E35" s="3">
         <v>584400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>591300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>847600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>874800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>604900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>604300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>772000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>755300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>436300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>504300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>626300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>586200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>307100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>439100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>547900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>509300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>260200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>317800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>405700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>464700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>235200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>244700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>400600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>238800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>296100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>458800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>456100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>199900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>254000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>515100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>448100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1318300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1074200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1763300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1125800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>774200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>860500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1590100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1470000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>874600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>849900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1095300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>960000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>663600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>692900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1220500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1080200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1090200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1348400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2159200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2738800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2912400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2838000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3289900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3190100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2366800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2647700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1278600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>830900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>875600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1907400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>903400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1022500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>969500</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3737,14 +3827,14 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>457600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>451200</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3757,12 +3847,12 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
@@ -3814,412 +3904,427 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4907700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4235200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3700300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4065500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4070800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3594100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3517500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3856200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3925300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3405200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3415200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3369600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3423900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2822000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2780100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2867400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2758200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2429800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2429400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2432300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2532100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2159400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2202100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2312600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2316400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2091800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2184600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2968900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3108300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2710300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2679200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2752100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2946900</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2616900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2398800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2103600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2355300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2361000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2220900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1971500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2033400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2203500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2382700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2152100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2191800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2355800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2343700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1993800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1949200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1886900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1872300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1530800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1482800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1386300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1373100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1189200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1229200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1353000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1463700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1278600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1890600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1950500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1983700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1677800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1821400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1733300</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>163900</v>
+      </c>
+      <c r="E45" s="3">
         <v>292700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>295800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>312900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>258800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>258700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>282500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>259400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>249400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>207300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>205500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>231700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>216200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>384800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>402300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>389900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>380000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>351500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>337500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>294300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>251600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>224400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>241600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>308500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>356600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4552000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>412700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>417100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>483300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>471600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>486600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>512000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9006800</v>
+      </c>
+      <c r="E46" s="3">
         <v>8000900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7863000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7859500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7506200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6934300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7337800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8099700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7714000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6887200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6869900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6726900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6675000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6074800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6379200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6299100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6125200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6030500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6470900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6991400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7125100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>6622100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6905600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6973500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6344700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6559800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9293800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6103100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6351500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7084700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5732000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6082600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6161700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4274,8 +4379,8 @@
       <c r="T47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -4319,210 +4424,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2392700</v>
+      </c>
+      <c r="E48" s="3">
         <v>2339900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3061000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2210700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2177500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2068700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2627100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1906600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1827800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1788300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2285300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1683800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1654700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1582300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1536100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1432100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1425900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1422200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1835600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1336700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1324900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1327700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1758500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1753600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1755200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1779900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1352000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1779100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1794100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1738400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1730800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1673400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1646800</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10550000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10520600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9693700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9715700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9755000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9698600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9436100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9578900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9409300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9450600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9535100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9056800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9136400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8754000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8767700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8611400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8739100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8767700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8810400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8508500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>8561500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>8568100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8629200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8377300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8348000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8371300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>8449300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>10887200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>11089900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>9577100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>9594200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>9668700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9706000</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1976100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1893400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>803000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1587900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1551800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1415800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>745700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1318500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1248100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1215100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>701600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1189400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1196500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1247400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1398600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1397200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1390600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1416500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>942900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1365600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1357900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1306900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>863400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>835000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>775700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>924600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1397200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1537500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1432100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1380800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>857900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>879800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>863400</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23925600</v>
+      </c>
+      <c r="E54" s="3">
         <v>22754800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21420700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21373800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20990500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20117400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20146700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20903700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20199200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19341200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19391900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18903200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18906500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17897400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18081600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17739800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17680800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17636900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18059800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18202200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>18369400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17824800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>18156700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17939400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17223600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17635600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>20492300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20306900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>20667600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>19781000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>17914900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>18304500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>18377900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5230,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2976100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2416900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2153900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2396600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2528600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2265200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2148000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2194800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2180100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2008300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2025200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2093300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2176900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1962600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2091600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2061300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1931600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1787300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1757800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1833200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1608900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1520200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1458800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1368200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1446700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1381300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1758800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1889900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1800100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1705300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1748700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1832100</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5210,52 +5344,52 @@
         <v>693100</v>
       </c>
       <c r="E58" s="3">
+        <v>693100</v>
+      </c>
+      <c r="F58" s="3">
         <v>915000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>694700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>694600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>851700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>625700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>952200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>952000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>902100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>957300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>348300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>550200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>348300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1048000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1049900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1049800</v>
-      </c>
-      <c r="T58" s="3">
-        <v>350400</v>
       </c>
       <c r="U58" s="3">
         <v>350400</v>
@@ -5264,450 +5398,465 @@
         <v>350400</v>
       </c>
       <c r="W58" s="3">
-        <v>475400</v>
+        <v>350400</v>
       </c>
       <c r="X58" s="3">
         <v>475400</v>
       </c>
       <c r="Y58" s="3">
+        <v>475400</v>
+      </c>
+      <c r="Z58" s="3">
         <v>775600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>775100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>649900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>949700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>650300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>650500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>829200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>374400</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>350600</v>
       </c>
       <c r="AH58" s="3">
         <v>350600</v>
       </c>
       <c r="AI58" s="3">
+        <v>350600</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>599600</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2581800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2370600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1754500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1673400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1656100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1622100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1639700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1693300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1623200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1665800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1582600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1409600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1381200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1340600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2547200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2434300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2580300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2312400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2614700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2205300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2204300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2090300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2043100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1936200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1811100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1844400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3207000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2366800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2461100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2314000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2259800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2224700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2321000</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8390900</v>
+      </c>
+      <c r="E60" s="3">
         <v>7305600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6286700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6523300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6799300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6367200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6068900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6628900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6592400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6101900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6053500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5214200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5593200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4831400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5686800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5545500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5630300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4594400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4752400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4313500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4512900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>4174600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>4338900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4170100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3829200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4240800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>5238600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4776100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5180200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4488500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4315700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4324000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4752700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3923700</v>
+      </c>
+      <c r="E61" s="3">
         <v>3922900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4524800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3921200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3920400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3919600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4759300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4317100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4316200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3978700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4345200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4476300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4476600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4481800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3788300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3787500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3786700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4492600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4491700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4490700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4489800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4496300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4496500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4494200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4618200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4624800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4922900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4921900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4920600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5226500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3740700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3739800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3738900</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>743100</v>
+      </c>
+      <c r="E62" s="3">
         <v>739000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>259000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>689500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>680500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>601000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>304200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>544300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>503500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>579700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>393300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>475900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>480300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>531400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2501300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2538400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2524500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2533400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2542600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2910300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2894000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2841100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2894200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2894100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2816700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2980200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3018400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3329800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3393900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3143200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>2793700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2897500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>3062600</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15280500</v>
+      </c>
+      <c r="E66" s="3">
         <v>14142300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12819800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13027500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13135300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12599900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12659800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13289400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13231600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12430400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12374900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12202800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12629300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11843100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11993000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11881500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11957300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11638300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11803900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11727100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11912100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11528100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11749000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11572700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11286700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>11863000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13224700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13069300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13537100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>12895200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>10892200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>10996400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>11590800</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10525600</v>
+      </c>
+      <c r="E72" s="3">
         <v>10491000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10422100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>10313900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9807600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9703100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9791800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9697600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>9194700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>9104200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9133700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8970900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8445400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8202300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8320900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>8320400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>8003700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>8098700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>8353200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>8626500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>8566200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>8452300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>8495300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>8489300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>8222100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>8127900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>9730800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>9762700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>9497200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9298300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>9439800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9624800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>9109900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8622900</v>
+      </c>
+      <c r="E76" s="3">
         <v>8590900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8579200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8326300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7834200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7491000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7457400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7591500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6947300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6889700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6995200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6681800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6258800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6036100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6088600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5858300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5723500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5998600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6255900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6475100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6457300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6296700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6407700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6366700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5936900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5772600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7267600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7237600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7130500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6885800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7022700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7308100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6787100</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>925700</v>
+      </c>
+      <c r="E81" s="3">
         <v>584400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>591300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>847600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>874800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>604900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>604300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>772000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>755300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>436300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>504300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>626300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>586200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>307100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>439100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>547900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>509300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>260200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>317800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>405700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>464700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>235200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>244700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>400600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>238800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>296100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>458800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>456100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>199900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>254000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>515100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>448100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E83" s="3">
         <v>52000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>12800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>51400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>46600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>46600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>44900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>48100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>43800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>43500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>82600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>83900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>79800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>77300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>76400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>72200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>74800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>76000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>70600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>74500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>74200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>75000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>105600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>104900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>97600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>89300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>88500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>85200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>94400</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1087700</v>
+      </c>
+      <c r="E89" s="3">
         <v>626200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1158900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1004000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>692100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>339500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>899900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1302600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>695900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>247200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>934800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>922300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>524000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>760300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>510200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>421700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-188200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>427100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>410600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>490500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>260100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>626900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>930500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>205200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-327600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>866400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>659400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>446300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-52600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>510400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>519700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>443900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-76400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-79700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-105800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-68400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-89900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-118900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-125600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-88300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-72900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-83800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-83500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-83200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-56900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-77100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-89000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-58900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-69100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-74800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-101400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-44100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-33600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-43900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-57100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-29500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-24900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-34700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-67900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-69500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-55900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-60800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-114400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-87800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-110600</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-146600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-755700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-85400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-68600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-385100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>323700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-260000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-544900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-81700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-436100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-89100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-556000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-91000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-214600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-67100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-175400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-83300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-336900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-46700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-48400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-113700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-237400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-68300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-40500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-126700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1510900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-108800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-75700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-187200</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +8819,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>231700</v>
+      </c>
+      <c r="E96" s="3">
         <v>231500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>208200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>209100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>210100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>209900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>188700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>189400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>189900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>189500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>170700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>171600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>171100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>170300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-153200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-156100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-155000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-155900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-139200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-140300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-141400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-140200</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-127000</v>
       </c>
       <c r="Z96" s="3">
         <v>-127000</v>
       </c>
       <c r="AA96" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-127400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-125900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-127000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-123700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-131700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-127700</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-128300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-129400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-110200</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-697200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-546000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-438700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-576200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-757800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-723100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1030400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-485900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-117600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-386700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-398200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-515700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>22800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-459200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-439200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-411400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-467000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-534600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-662600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-527400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-382700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-554900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-346600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-103700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-434800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1769400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-344100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-544700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>29200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1130100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-509900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-377500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-395000</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E101" s="3">
         <v>39100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-73100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>38700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-24200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>34800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-21100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-20100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>14100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>33800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-41700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-37500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>33800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-41700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-37500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-7200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-10100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>15000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-43400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>56900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>26500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>17000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-32200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>16400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-32700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-10800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-13500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-67300</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>244100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-689100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>637500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>351600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-86300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-729600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>120100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>595400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>24700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-245400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>135300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>296400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-29300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-527600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>140300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-258200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-810800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-579600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-173600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>74400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-451900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>99800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>823300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-280900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1369100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>472700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-44700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1031800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1004000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-119100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>53000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-205600</v>
       </c>
     </row>
